--- a/output/sliding_window_results_window_4.xlsx
+++ b/output/sliding_window_results_window_4.xlsx
@@ -460,16 +460,16 @@
         <v>19</v>
       </c>
       <c r="B2" t="n">
-        <v>30.21</v>
+        <v>36.3</v>
       </c>
       <c r="C2" t="n">
-        <v>28.96282475924779</v>
+        <v>35.7417208821746</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.247175240752213</v>
+        <v>-0.5582791178253927</v>
       </c>
       <c r="E2" t="n">
-        <v>1.555446081145341</v>
+        <v>0.3116755733998988</v>
       </c>
     </row>
     <row r="3">
@@ -477,16 +477,16 @@
         <v>18</v>
       </c>
       <c r="B3" t="n">
-        <v>30.48</v>
+        <v>38.5</v>
       </c>
       <c r="C3" t="n">
-        <v>29.78177514306905</v>
+        <v>39.73656224717653</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.6982248569309526</v>
+        <v>1.236562247176529</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4875179508362492</v>
+        <v>1.529086191142268</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>17</v>
       </c>
       <c r="B4" t="n">
-        <v>30.95</v>
+        <v>40.1</v>
       </c>
       <c r="C4" t="n">
-        <v>30.48192191517216</v>
+        <v>43.39036405151685</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.468078084827841</v>
+        <v>3.290364051516853</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2190970934960995</v>
+        <v>10.8264955915144</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>16</v>
       </c>
       <c r="B5" t="n">
-        <v>31.38</v>
+        <v>41.5</v>
       </c>
       <c r="C5" t="n">
-        <v>31.37574682189717</v>
+        <v>44.44146595000356</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.004253178102832322</v>
+        <v>2.941465950003561</v>
       </c>
       <c r="E5" t="n">
-        <v>1.808952397441235e-05</v>
+        <v>8.652221935030353</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>15</v>
       </c>
       <c r="B6" t="n">
-        <v>32.28</v>
+        <v>43.7</v>
       </c>
       <c r="C6" t="n">
-        <v>31.87655543529906</v>
+        <v>49.83873553065419</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4034445647009406</v>
+        <v>6.138735530654188</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1627675167867314</v>
+        <v>37.68407391531616</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>33.1</v>
+        <v>48.1</v>
       </c>
       <c r="C7" t="n">
-        <v>32.38999164430697</v>
+        <v>54.53601661703924</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7100083556930343</v>
+        <v>6.436016617039243</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5041118651539264</v>
+        <v>41.42230989480527</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>13</v>
       </c>
       <c r="B8" t="n">
-        <v>34.4</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>34.14498445038662</v>
+        <v>60.1716691518429</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2550155496133826</v>
+        <v>7.171669151842899</v>
       </c>
       <c r="E8" t="n">
-        <v>0.06503293054461559</v>
+        <v>51.43283842349504</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>36.3</v>
+        <v>56.1</v>
       </c>
       <c r="C9" t="n">
-        <v>35.36071504418643</v>
+        <v>64.06658688422348</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9392849558135623</v>
+        <v>7.966586884223481</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8822562282176857</v>
+        <v>63.4665065838816</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>11</v>
       </c>
       <c r="B10" t="n">
-        <v>38.5</v>
+        <v>60</v>
       </c>
       <c r="C10" t="n">
-        <v>37.67701745633499</v>
+        <v>63.81223314230189</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8229825436650131</v>
+        <v>3.812233142301892</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6773002671773352</v>
+        <v>14.53312153126496</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>40.1</v>
+        <v>63.9</v>
       </c>
       <c r="C11" t="n">
-        <v>39.33913197005448</v>
+        <v>69.56128482228357</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7608680299455202</v>
+        <v>5.661284822283569</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5789201589931769</v>
+        <v>32.05014583901831</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>9</v>
       </c>
       <c r="B12" t="n">
-        <v>41.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="C12" t="n">
-        <v>40.86759325345918</v>
+        <v>74.40903348255242</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.6324067465408163</v>
+        <v>3.809033482552422</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3999382930703403</v>
+        <v>14.50873607120544</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>8</v>
       </c>
       <c r="B13" t="n">
-        <v>43.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="C13" t="n">
-        <v>44.33827370465383</v>
+        <v>84.19096804136427</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6382737046538267</v>
+        <v>3.290968041364266</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4073933220525204</v>
+        <v>10.83047064928095</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>7</v>
       </c>
       <c r="B14" t="n">
-        <v>48.1</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="C14" t="n">
-        <v>45.91381017728222</v>
+        <v>86.48872551229985</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.186189822717786</v>
+        <v>-2.611274487700143</v>
       </c>
       <c r="E14" t="n">
-        <v>4.779425940954825</v>
+        <v>6.818754450113645</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>6</v>
       </c>
       <c r="B15" t="n">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="C15" t="n">
-        <v>52.33104212777322</v>
+        <v>86.77599270398829</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.6689578722267839</v>
+        <v>-8.224007296011706</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4475046348141862</v>
+        <v>67.63429600485378</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>5</v>
       </c>
       <c r="B16" t="n">
-        <v>56.1</v>
+        <v>98.8</v>
       </c>
       <c r="C16" t="n">
-        <v>55.60792169860623</v>
+        <v>97.72680857064356</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.492078301393768</v>
+        <v>-1.073191429356442</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2421410547025759</v>
+        <v>1.151739844044122</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>4</v>
       </c>
       <c r="B17" t="n">
-        <v>60</v>
+        <v>103.3</v>
       </c>
       <c r="C17" t="n">
-        <v>59.00333259746108</v>
+        <v>100.1722567027717</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.9966674025389182</v>
+        <v>-3.127743297228292</v>
       </c>
       <c r="E17" t="n">
-        <v>0.993345911283674</v>
+        <v>9.78277813335651</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>3</v>
       </c>
       <c r="B18" t="n">
-        <v>63.9</v>
+        <v>107</v>
       </c>
       <c r="C18" t="n">
-        <v>61.56551386764008</v>
+        <v>108.1075953352422</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.33448613235992</v>
+        <v>1.107595335242195</v>
       </c>
       <c r="E18" t="n">
-        <v>5.44982550218078</v>
+        <v>1.22676742665027</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>2</v>
       </c>
       <c r="B19" t="n">
-        <v>70.59999999999999</v>
+        <v>108.7</v>
       </c>
       <c r="C19" t="n">
-        <v>69.98757664262568</v>
+        <v>118.9948150868499</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6124233573743112</v>
+        <v>10.29481508684988</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3750623686576233</v>
+        <v>105.9832176724319</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>1</v>
       </c>
       <c r="B20" t="n">
-        <v>80.90000000000001</v>
+        <v>112.7</v>
       </c>
       <c r="C20" t="n">
-        <v>79.71466425508343</v>
+        <v>121.1054694179412</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.185335744916571</v>
+        <v>8.405469417941148</v>
       </c>
       <c r="E20" t="n">
-        <v>1.405020828176923</v>
+        <v>70.65191613594391</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>0</v>
       </c>
       <c r="B21" t="n">
-        <v>89.09999999999999</v>
+        <v>117.2</v>
       </c>
       <c r="C21" t="n">
-        <v>87.77252488869235</v>
+        <v>130.7910867715849</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.327475111307649</v>
+        <v>13.5910867715849</v>
       </c>
       <c r="E21" t="n">
-        <v>1.762190171141255</v>
+        <v>184.71763963275</v>
       </c>
     </row>
     <row r="22">
@@ -803,11 +803,11 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>-16.10708214676799</v>
+        <v>69.55939090445506</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>21.39431620890984</v>
+        <v>735.2147914994987</v>
       </c>
     </row>
     <row r="23">
@@ -820,7 +820,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>1.069715810445492</v>
+        <v>36.76073957497493</v>
       </c>
     </row>
   </sheetData>
